--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.47269961252454</v>
+        <v>3.164313687035238</v>
       </c>
       <c r="D2" t="n">
-        <v>19.72104331513781</v>
+        <v>3.204669538709894</v>
       </c>
       <c r="E2" t="n">
-        <v>5.954166282370692</v>
+        <v>0.9675520208852376</v>
       </c>
       <c r="F2" t="n">
-        <v>5.301211321348092</v>
+        <v>0.861446839719065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.15564437074637</v>
+        <v>3.275292210246286</v>
       </c>
       <c r="D3" t="n">
-        <v>30.20581667479045</v>
+        <v>4.908445209653448</v>
       </c>
       <c r="E3" t="n">
-        <v>5.954166282370692</v>
+        <v>0.9675520208852376</v>
       </c>
       <c r="F3" t="n">
-        <v>5.301211321348092</v>
+        <v>0.861446839719065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.02223948184644</v>
+        <v>3.741113915800046</v>
       </c>
       <c r="D4" t="n">
-        <v>23.39670890736404</v>
+        <v>3.801965197446657</v>
       </c>
       <c r="E4" t="n">
-        <v>5.954166282370692</v>
+        <v>0.9675520208852376</v>
       </c>
       <c r="F4" t="n">
-        <v>5.301211321348092</v>
+        <v>0.861446839719065</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.98645316260862</v>
+        <v>2.4352986389239</v>
       </c>
       <c r="D5" t="n">
-        <v>15.0495955420033</v>
+        <v>2.445559275575536</v>
       </c>
       <c r="E5" t="n">
-        <v>5.954166282370692</v>
+        <v>0.9675520208852376</v>
       </c>
       <c r="F5" t="n">
-        <v>5.301211321348092</v>
+        <v>0.861446839719065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.988914278718044</v>
+        <v>0.9731985702916821</v>
       </c>
       <c r="D6" t="n">
-        <v>26.80511553344649</v>
+        <v>4.355831274185055</v>
       </c>
       <c r="E6" t="n">
-        <v>5.954166282370692</v>
+        <v>0.9675520208852376</v>
       </c>
       <c r="F6" t="n">
-        <v>5.301211321348092</v>
+        <v>0.861446839719065</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
